--- a/dictionaries/SneakPeak.xlsx
+++ b/dictionaries/SneakPeak.xlsx
@@ -371,7 +371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B452"/>
+  <dimension ref="A1:B465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1996,2953 +1996,3044 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Enchantment</t>
+          <t>Emination:%</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Encounter</t>
+          <t>Enchantment</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>تجهیزات</t>
+          <t>Encounter</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Evil</t>
+          <t>Enemy</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Exhaustion</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>خستگی</t>
+          <t>تجهیزات</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ExperiencePoint</t>
+          <t>Evil</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ExperiencePoints</t>
+          <t>Exhaustion</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>خستگی</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Experties</t>
+          <t>ExperiencePoint</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Exploration</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>گشت و گذار</t>
+          <t>ExperiencePoints</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Falling</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>سقوط</t>
+          <t>Experties</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Exploration</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ویژگی</t>
+          <t>گشت و گذار</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Fiend</t>
+          <t>Falling</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>سقوط</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Fighter</t>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>ویژگی</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Finesse</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>فینس</t>
+          <t>Fiend</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Fire</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>آتشی</t>
+          <t>Fighter</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FireDamage</t>
+          <t>Finesse</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>آسیب آتشی</t>
+          <t>فینس</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FireResistance</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>مقاومت به آتش</t>
+          <t>آتشی</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FlySpeed</t>
+          <t>FireDamage</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>سرعت پرواز</t>
+          <t>آسیب آتشی</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ForgottenRealms</t>
+          <t>FireResistance</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>فورگاتن رلمز</t>
+          <t>مقاومت به آتش</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Friendly</t>
+          <t>FlySpeed</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>دوستانه</t>
+          <t>سرعت پرواز</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Frightened</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>ترسیده</t>
+          <t>Force</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Gargantuan</t>
+          <t>ForgottenRealms</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>غول آسا</t>
+          <t>فورگاتن رلمز</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Gargoyle</t>
+          <t>Friendly</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Gargoyle</t>
+          <t>دوستانه</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Giant</t>
+          <t>Frightened</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>ترسیده</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Goblin</t>
+          <t>Gargantuan</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>غول آسا</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Gargoyle</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Gargoyle</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Grapple</t>
+          <t>Giant</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Grappled</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>گرفته‌شده</t>
+          <t>Goblin</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Grayhawk</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>گری‌هاوک</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Griffon</t>
+          <t>Grapple</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Grappled</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>گرفته‌شده</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HalfCover</t>
+          <t>Grayhawk</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>پوشش نصفه</t>
+          <t>گری‌هاوک</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Hazard</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>مخاطره</t>
+          <t>Griffon</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Healing</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>شفا بخشیدن</t>
+          <t>HP</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>HeavilyObscured</t>
+          <t>HalfCover</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>به شدت پوشیده</t>
+          <t>پوشش نصفه</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Help</t>
+          <t>Hazard</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>کمک‌کردن</t>
+          <t>مخاطره</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>HeroicInspiration</t>
+          <t>Healing</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>الهام قهرمانانه</t>
+          <t>شفا بخشیدن</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Hide</t>
+          <t>HeavilyObscured</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>قایم شدن</t>
+          <t>به شدت پوشیده</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>History</t>
+          <t>Help</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>تاریخ</t>
+          <t>کمک‌کردن</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>HitDice</t>
+          <t>HeroicInspiration</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>الهام قهرمانانه</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>HitDie</t>
+          <t>Hide</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>قایم شدن</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>HitPoint</t>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>HitPointDice</t>
+          <t>HitDice</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>HitPoints</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>جان</t>
+          <t>HitDie</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HitPointsMaximum</t>
+          <t>HitPoint</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Hostile</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>خصمانه</t>
+          <t>HitPointDice</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Huge</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>گنده</t>
+          <t>HitPointDie</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Humanoid</t>
+          <t>HitPoints</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>جان</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Illusion</t>
+          <t>HitPointsMaximum</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Immunity</t>
+          <t>Hostile</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>مصونیت</t>
+          <t>خصمانه</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Improvised</t>
+          <t>Hover</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Incapacitated</t>
+          <t>Huge</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ناتوان</t>
+          <t>گنده</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Index</t>
+          <t>Humanoid</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Indifferent</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>بی‌تفاوت</t>
+          <t>Illusion</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Infernal</t>
+          <t>Immunity</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>اینفرنال</t>
+          <t>مصونیت</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Influence</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>تأثیر گذاشتن</t>
+          <t>Improvised</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Initiative</t>
+          <t>Incapacitated</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ترتیب نوبت</t>
+          <t>ناتوان</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>InitiativeOrder</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>ترتیب نوبت</t>
+          <t>Index</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>InitiativeRoll</t>
+          <t>Indifferent</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>تاس ترتیب</t>
+          <t>بی‌تفاوت</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Infernal</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>بینش</t>
+          <t>اینفرنال</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Int</t>
+          <t>Influence</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>تأثیر گذاشتن</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Intelligence</t>
+          <t>Initiative</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>هوش</t>
+          <t>ترتیب نوبت</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>IntelligenceCheck</t>
+          <t>InitiativeOrder</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>چک هوش</t>
+          <t>ترتیب نوبت</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Intimidation</t>
+          <t>InitiativeRoll</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ارعاب</t>
+          <t>تاس ترتیب</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Investigation</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>تحقیق</t>
+          <t>بینش</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Invisible</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>نامرئی</t>
+          <t>Int</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Intelligence</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>آیتم</t>
+          <t>هوش</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Jumping</t>
+          <t>IntelligenceCheck</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>پرش</t>
+          <t>چک هوش</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>Intimidation</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ارعاب</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Investigation</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>تحقیق</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>Invisible</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>نامرئی</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>بزرگ</t>
+          <t>آیتم</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Lawful</t>
+          <t>Jumping</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>پرش</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>LawfulEvil</t>
+          <t>LE</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>LawfulGood</t>
+          <t>LG</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>LawfulNeuteral</t>
+          <t>LN</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>LawfulNeutral</t>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>بزرگ</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>سطح</t>
+          <t>Lawful</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>LightlyObscured</t>
-        </is>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>کم پوشیده</t>
+          <t>LawfulEvil</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Lightning</t>
+          <t>LawfulGood</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>LawfulNeuteral</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Line:%:%</t>
+          <t>LawfulNeutral</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>LongRange</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>برد بلند</t>
+          <t>سطح</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>LongRest</t>
+          <t>LightlyObscured</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>استراحت طولانی</t>
+          <t>کم پوشیده</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Lightning</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Magic</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>جادو</t>
+          <t>Line</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>MagicItem</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>آیتم جادویی</t>
+          <t>Line:%:%</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>MagicItems</t>
+          <t>LongRange</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>آیتم‌های جادویی</t>
+          <t>برد بلند</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Magical</t>
+          <t>LongRest</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>جادویی</t>
+          <t>استراحت طولانی</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Malnutrition</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>کم غذایی</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>MarchingOrder</t>
+          <t>Magic</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ترتیب حرکت</t>
+          <t>جادو</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>MagicItem</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>آیتم جادویی</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>MaterialComponent</t>
+          <t>MagicItems</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>آیتم‌های جادویی</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>MaterialComponents</t>
+          <t>Magical</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>جادویی</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MaterialPlane</t>
+          <t>Malnutrition</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>کم غذایی</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MaximumHitPoint</t>
+          <t>MarchingOrder</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>بیشینه جان</t>
+          <t>ترتیب حرکت</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>MaximumHitPoints</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>بیشینه‌های جان</t>
+          <t>Material</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Medicine</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>پزشکی</t>
+          <t>MaterialComponent</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>متوسط</t>
+          <t>MaterialComponents</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>MeleeAttack</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>حمله نزدیک‌زن</t>
+          <t>MaterialPlane</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>MeleeAttacks</t>
+          <t>MaximumHitPoint</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>حملات نزدیک‌زن</t>
+          <t>بیشینه جان</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>MeleeWeapon</t>
+          <t>MaximumHitPoints</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>سلاح نزدیک‌زن</t>
+          <t>بیشینه‌های جان</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Miniature</t>
+          <t>Medicine</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>مینی</t>
+          <t>پزشکی</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Modifier</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>مودیفایر</t>
+          <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Modifiers</t>
+          <t>MeleeAttack</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>حمله نزدیک‌زن</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Monk</t>
+          <t>MeleeAttacks</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>حملات نزدیک‌زن</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Monster</t>
+          <t>MeleeWeapon</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>هیولا</t>
+          <t>سلاح نزدیک‌زن</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Mount</t>
+          <t>Miniature</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>مینی</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Movement</t>
+          <t>Modifier</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>جابه‌جایی</t>
+          <t>مودیفایر</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>MovementAndPosition</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>حرکت و موقعیت</t>
+          <t>Modifiers</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Multiclass</t>
+          <t>Monk</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Multiclassing</t>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>هیولا</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Multiverse</t>
+          <t>Mount</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>جابه‌جایی</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>MovementAndPosition</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>حرکت و موقعیت</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>NG</t>
+          <t>Multiclass</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>NPC</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>NPC</t>
+          <t>Multiclassing</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Natural1</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>۱ طبیعی</t>
+          <t>Multiverse</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Natural20</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>۲۰ طبیعی</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Nature</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>دانش طبیعت</t>
+          <t>NE</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Necromancy</t>
+          <t>NG</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>NecroticDamage</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>آسیب پوسیدگی</t>
+          <t>NPC</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Neuteral</t>
+          <t>Natural1</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>۱ طبیعی</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>NeuteralEvil</t>
+          <t>Natural20</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>۲۰ طبیعی</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>NeuteralGood</t>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>دانش طبیعت</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Necromancy</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>NeutralEvil</t>
+          <t>Necrotic</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>NeutralGood</t>
+          <t>NecroticDamage</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>آسیب پوسیدگی</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>NonHumanoid</t>
+          <t>Neuteral</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>NonMagical</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr">
-        <is>
-          <t>غیرجادویی</t>
+          <t>NeuteralEvil</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>NonPlayerCharacter</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>کاراکتر غیربازیکن</t>
+          <t>NeuteralGood</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>NormalRange</t>
-        </is>
-      </c>
-      <c r="B289" t="inlineStr">
-        <is>
-          <t>برد طبیعی</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="B290" t="inlineStr">
-        <is>
-          <t>جسم</t>
+          <t>NeutralEvil</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Objects</t>
-        </is>
-      </c>
-      <c r="B291" t="inlineStr">
-        <is>
-          <t>اجسام</t>
+          <t>NeutralGood</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Obscured</t>
-        </is>
-      </c>
-      <c r="B292" t="inlineStr">
-        <is>
-          <t>پوشیده</t>
+          <t>NonHumanoid</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>OneShot</t>
+          <t>NonMagical</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>وان شات</t>
+          <t>غیرجادویی</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>OpportunityAttack</t>
+          <t>NonPlayerCharacter</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>فرصت حمله</t>
+          <t>کاراکتر غیربازیکن</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>OpportunityAttacks</t>
+          <t>NormalRange</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>فرصت‌های حمله</t>
+          <t>برد طبیعی</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>OppurtunityAttack</t>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>جسم</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>PB</t>
+          <t>Objects</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>اجسام</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Paladin</t>
+          <t>Obscured</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>پوشیده</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Paralyzed</t>
+          <t>OneShot</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>فلج</t>
+          <t>وان شات</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>PassivePerception</t>
+          <t>OpportunityAttack</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>فرصت حمله</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Perception</t>
+          <t>OpportunityAttacks</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>ادراک</t>
+          <t>فرصت‌های حمله</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>اجرا هنری</t>
+          <t>OppurtunityAttack</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Persuasion</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>متقاعدسازی</t>
+          <t>Origin</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Petrified</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>سنگ‌شده</t>
+          <t>OuterPlanes</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>PiercingDamage</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>آسیب سوراخ‌کننده</t>
+          <t>PB</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Plane</t>
+          <t>Paladin</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>PlanesOfExistence</t>
+          <t>Paralyzed</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>صفحات وجودی</t>
+          <t>فلج</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="B308" t="inlineStr">
-        <is>
-          <t>بازیکن</t>
+          <t>PassivePerception</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>PlayerCharacter</t>
+          <t>Perception</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>کاراکتر بازیکن</t>
+          <t>ادراک</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>PlayerCharacters</t>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>اجرا هنری</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>PlayerHandbook</t>
+          <t>Persuasion</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>پلیرز هندبوک</t>
+          <t>متقاعدسازی</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>PointCost</t>
+          <t>Petrified</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>سنگ‌شده</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>PoisonDamage</t>
+          <t>PiercingDamage</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>آسیب سوراخ‌کننده</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Poisoned</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr">
-        <is>
-          <t>مسموم</t>
+          <t>Plane</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>PlanesOfExistence</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>موقعیت</t>
+          <t>صفحات وجودی</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Prepare</t>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>بازیکن</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Prepared</t>
+          <t>PlayerCharacter</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>کاراکتر بازیکن</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>PreparedSpells</t>
+          <t>PlayerCharacters</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Primal</t>
+          <t>PlayerHandbook</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>پلیرز هندبوک</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>PrimaryAbility</t>
+          <t>PointCost</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Proficiency</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>مهارت</t>
+          <t>PoisonDamage</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ProficiencyBonus</t>
+          <t>Poisoned</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>امتیاز مهارت</t>
+          <t>مسموم</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Prone</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>افتاده</t>
+          <t>موقعیت</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Property</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>ویژگی</t>
+          <t>Prepare</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Psychic</t>
+          <t>Prepared</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>PreparedSpells</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>RadiantDamage</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr">
-        <is>
-          <t>آسیب تابش الهی</t>
+          <t>Primal</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>RandomGeneration</t>
+          <t>PrimaryAbility</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Range</t>
+          <t>Proficiency</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>برد</t>
+          <t>مهارت</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Range:%</t>
+          <t>ProficiencyBonus</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>امتیاز مهارت</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>RangedAttack</t>
+          <t>Prone</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>حمله پرتابی</t>
+          <t>افتاده</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>RangedAttacks</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>حملات پرتابی</t>
+          <t>ویژگی</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>RangedWeapon</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr">
-        <is>
-          <t>سلاح پرتابی</t>
+          <t>Psychic</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Ranger</t>
+          <t>R</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Reach</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>طول</t>
+          <t>Radiant</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Reaction</t>
+          <t>RadiantDamage</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>واکنش</t>
+          <t>آسیب تابش الهی</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>آماده کردن</t>
+          <t>RandomGeneration</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Realms</t>
+          <t>Range</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>جهان‌ها</t>
+          <t>برد</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Religion</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>دانش دینی</t>
+          <t>Range:%</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Restrained</t>
+          <t>RangedAttack</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>محبوس</t>
+          <t>حمله پرتابی</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Rogue</t>
+          <t>RangedAttacks</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>روگ</t>
+          <t>حملات پرتابی</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>RangedWeapon</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>دور</t>
+          <t>سلاح پرتابی</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>RulesGlossary</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>فهرست قوانین</t>
+          <t>Ranger</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>طول</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Reaction</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>سیو</t>
+          <t>واکنش</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>SavingThrow</t>
+          <t>Ready</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>سیوینگ ثرو</t>
+          <t>آماده کردن</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>SavingThrows</t>
+          <t>Realms</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>سیوینگ ثروها</t>
+          <t>جهان‌ها</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Religion</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>دانش دینی</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Restrained</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>اسکور</t>
+          <t>محبوس</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr">
-        <is>
-          <t>جست‌وجو کردن</t>
+          <t>Ritual</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Session</t>
+          <t>Rogue</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>روگ</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Shadowfell</t>
+          <t>Round</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>دور</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ShortOrLongRest</t>
+          <t>RulesGlossary</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>استراحت کوتاه یا طولانی</t>
+          <t>فهرست قوانین</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ShortRest</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t>استراحت کوتاه</t>
+          <t>S</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Sigil</t>
+          <t>Save</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>سیو</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>SavingThrow</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>اندازه</t>
+          <t>سیوینگ ثرو</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>SizeCategory</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>دسته اندازه</t>
+          <t>SavingThrowProficiencies</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Skill</t>
+          <t>SavingThrows</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>توانایی</t>
+          <t>سیوینگ ثروها</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>SkillProficiencies</t>
+          <t>School</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>SkillProficiency</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>مهارت در توانایی</t>
+          <t>اسکور</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Slashing</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>برشی</t>
+          <t>جست‌وجو کردن</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>SlashingDamage</t>
+          <t>Session</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>SleightOfHand</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr">
-        <is>
-          <t>چابکی دست</t>
+          <t>Shadowfell</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>ShortOrLongRest</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>کوچک</t>
+          <t>استراحت کوتاه یا طولانی</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>SocialInteraction</t>
+          <t>ShortRest</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>تعامل اجتماعی</t>
+          <t>استراحت کوتاه</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Somatic</t>
+          <t>Sigil</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>SomaticComponent</t>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>اندازه</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Sorcerer</t>
+          <t>SizeCategory</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>دسته اندازه</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Species</t>
+          <t>Skill</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>گونه</t>
+          <t>توانایی</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr">
-        <is>
-          <t>سرعت</t>
+          <t>SkillProficiencies</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Spell</t>
+          <t>SkillProficiency</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>طلسم</t>
+          <t>مهارت در توانایی</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>SpellAttackBonus</t>
+          <t>Slashing</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>برشی</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>SpellCasting</t>
+          <t>SlashingDamage</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>SpellCastingClasses</t>
+          <t>SleightOfHand</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>چابکی دست</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>SpellSaveDC</t>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>کوچک</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>SpellSlot</t>
+          <t>SocialInteraction</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>اسلات طلسم</t>
+          <t>تعامل اجتماعی</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>SpellSlots</t>
+          <t>Somatic</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Spellcaster</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>اجراکننده طلسم</t>
+          <t>SomaticComponent</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Spellcasters</t>
+          <t>Sorcerer</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Spellcasting</t>
+          <t>Species</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>اجرای طلسم</t>
+          <t>گونه</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Sphere</t>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>سرعت</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Sprite</t>
+          <t>Spell</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>طلسم</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Stable</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>تثبیت</t>
+          <t>SpellAttackBonus</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Stablize</t>
+          <t>SpellCasting</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>StablizingACharacter</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>تثبیت کاراکتر</t>
+          <t>SpellCastingClasses</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>StandardArray</t>
+          <t>SpellSaveDC</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Stat</t>
+          <t>SpellSlot</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>اسلات طلسم</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>StatBlock</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>استت بلاک</t>
+          <t>SpellSlots</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Stealth</t>
+          <t>Spellcaster</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>مخفی‌کاری</t>
+          <t>اجراکننده طلسم</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Str</t>
+          <t>Spellcasters</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Strength</t>
+          <t>Spellcasting</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>قدرت</t>
+          <t>اجرای طلسم</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>StrengthCheck</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>چک قدرت</t>
+          <t>Sphere</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>StrengthModifier</t>
+          <t>Sprite</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>StrengthScore</t>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>تثبیت</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Study</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>مطالعه</t>
+          <t>Stablize</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Stunned</t>
+          <t>StablizingACharacter</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>گیج‌شده</t>
+          <t>تثبیت کاراکتر</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Subclass</t>
+          <t>StandardArray</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Suffocation</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>خفگی</t>
+          <t>Stat</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>StatBlock</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>سورپرایز</t>
+          <t>استت بلاک</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Survival</t>
+          <t>Stealth</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>بقا</t>
+          <t>مخفی‌کاری</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>SwimSpeed</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>سرعت شنا کردن</t>
+          <t>Str</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Swimming</t>
+          <t>Strength</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>شنا کردن</t>
+          <t>قدرت</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>StrengthCheck</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>هدف</t>
+          <t>چک قدرت</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Targets</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>اهداف</t>
+          <t>StrengthModifier</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Telekenises</t>
+          <t>StrengthSavingThrow</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>TemporaryHitPoint</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>جان موقت</t>
+          <t>StrengthScore</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>TemporaryHitPoints</t>
+          <t>Study</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>جان‌های موقت</t>
+          <t>مطالعه</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Terrain</t>
+          <t>Stunned</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>زمین</t>
+          <t>گیج‌شده</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ThievesTools</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>ابزار دزدان</t>
+          <t>Subclass</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>ThreeQuarterCover</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>پوشش سه‌چهارم</t>
+          <t>SubclassFeature</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>Suffocation</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>خفگی</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ThunderDamage</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>آسیب رعد</t>
+          <t>سورپرایز</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Tiny</t>
+          <t>Survival</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>کوچولو</t>
+          <t>بقا</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Tool</t>
+          <t>SwimSpeed</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>ابزار</t>
+          <t>سرعت شنا کردن</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>ToolProficiency</t>
+          <t>Swimming</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>شنا کردن</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>TotalCover</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>پوشش کامل</t>
+          <t>هدف</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Targets</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>اهداف</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Trait</t>
+          <t>Telekenises</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Tremorsense</t>
+          <t>TemporaryHitPoint</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Tremorsense</t>
+          <t>جان موقت</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>TemporaryHitPoints</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>ماشه</t>
+          <t>جان‌های موقت</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Trinket</t>
+          <t>Terrain</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>عتیقه</t>
+          <t>زمین</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Truesight</t>
+          <t>ThievesTools</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Truesight</t>
+          <t>ابزار دزدان</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Turn</t>
+          <t>ThreeQuarterCover</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>نوبت بازی</t>
+          <t>پوشش سه‌چهارم</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>TurnBased</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>نوبتی</t>
+          <t>Thunder</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Unaligned</t>
+          <t>ThunderDamage</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>آسیب رعد</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>UnarmedStrike</t>
+          <t>Tiny</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>ضربه غیرمسلحانه</t>
+          <t>کوچولو</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>UnarmedStrikes</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>ضربات غیرمسلحانه</t>
+          <t>ابزار</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Unconscious</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>بی‌هوش</t>
+          <t>ToolProficiency</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>TotalCover</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>پوشش کامل</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>UnoccupiedSpace</t>
+          <t>Training</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Unwilling</t>
+          <t>Trait</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Utilize</t>
+          <t>Tremorsense</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>استفاده</t>
+          <t>Tremorsense</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>ماشه</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Vehicle</t>
+          <t>Trinket</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>وسیله نقلیه</t>
+          <t>عتیقه</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Vehicles</t>
+          <t>Truesight</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>وسایل نقلیه</t>
+          <t>Truesight</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>VehiclesForSale</t>
+          <t>Turn</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>وسایل برای فروش</t>
+          <t>نوبت بازی</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Verbal</t>
+          <t>TurnBased</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>نوبتی</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>VerbalComponent</t>
+          <t>Unaligned</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Vision</t>
+          <t>UnarmedStrike</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>بینایی</t>
+          <t>ضربه غیرمسلحانه</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Vulnerability</t>
+          <t>UnarmedStrikes</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>آسیب‌پذیری</t>
+          <t>ضربات غیرمسلحانه</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Warlock</t>
+          <t>Unconscious</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>بی‌هوش</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Weapon</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t xml:space="preserve">سلاح </t>
+          <t>Undead</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>WeaponProficiencies</t>
+          <t>UnoccupiedSpace</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>WeaponProperties</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>ویژگی‌های اسلحه</t>
+          <t>Unwilling</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Willing</t>
+          <t>Utilize</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>راضی</t>
+          <t>استفاده</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Wis</t>
+          <t>V</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Wisdom</t>
+          <t>Vehicle</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>خرد</t>
+          <t>وسیله نقلیه</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>WisdomCheck</t>
+          <t>Vehicles</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>چک خرد</t>
+          <t>وسایل نقلیه</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>WisdomSavingThrow</t>
+          <t>VehiclesForSale</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>سیوینگ ثرو خرد</t>
+          <t>وسایل برای فروش</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>WisdomScore</t>
+          <t>Verbal</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Wizard</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>ویزارد</t>
+          <t>VerbalComponent</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
+        <is>
+          <t>Vision</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>بینایی</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Vulnerability</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>آسیب‌پذیری</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Warlock</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Weapon</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">سلاح </t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>WeaponProficiencies</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>WeaponProperties</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>ویژگی‌های اسلحه</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Willing</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>راضی</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Wis</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Wisdom</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>خرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>WisdomCheck</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>چک خرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>WisdomSavingThrow</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>سیوینگ ثرو خرد</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>WisdomScore</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Wizard</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>ویزارد</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
         <is>
           <t>XP</t>
         </is>
@@ -4959,7 +5050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4968,12 +5059,11 @@
           <t>Archfey</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GreatOldOne</t>
+          <t>Celestial(Warlock)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -4981,34 +5071,48 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Invocation</t>
-        </is>
-      </c>
+          <t>Fiend(Warlock)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PactMagic</t>
+          <t>GreatOldOne</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PactWeapon</t>
+          <t>Invocation</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Patron</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>PactMagic</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>PactWeapon</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Patron</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>ThirstingBlade</t>
         </is>
@@ -5034,7 +5138,6 @@
           <t>BattleMaster</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5042,7 +5145,6 @@
           <t>Champion</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5050,7 +5152,6 @@
           <t>CombatManuver</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5072,7 +5173,6 @@
           <t>PsiWarrior</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5080,7 +5180,6 @@
           <t>TwoExtraAttacks</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5102,6 +5201,7 @@
           <t>BeastMaster</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5109,6 +5209,7 @@
           <t>FeyWanderer</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5116,6 +5217,7 @@
           <t>GloomStalker</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5123,6 +5225,7 @@
           <t>Hunter</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5144,6 +5247,7 @@
           <t>Circle</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5151,6 +5255,7 @@
           <t>Land</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5158,6 +5263,7 @@
           <t>Moon</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5165,6 +5271,7 @@
           <t>Sea</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5172,6 +5279,7 @@
           <t>Stars</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5184,7 +5292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5193,6 +5301,7 @@
           <t>College</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5200,41 +5309,39 @@
           <t>Dance</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dextrity</t>
-        </is>
-      </c>
+          <t>Glamour</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Glamour</t>
-        </is>
-      </c>
+          <t>Lore</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lore</t>
-        </is>
-      </c>
+          <t>ToolProficiencies</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ToolProficiencies</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
           <t>Valor</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5256,7 +5363,6 @@
           <t>Devotion</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5264,7 +5370,6 @@
           <t>Glory</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5272,7 +5377,6 @@
           <t>Oath</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5280,7 +5384,6 @@
           <t>TheAncients</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5288,7 +5391,6 @@
           <t>Vengeance</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5301,7 +5403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5310,7 +5412,6 @@
           <t>Domain</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5318,35 +5419,40 @@
           <t>Life</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SearUndead</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Sear Undead</t>
-        </is>
-      </c>
+          <t>Light(Cleric)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Trickery</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>SearUndead</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sear Undead</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Trickery</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>War</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5368,6 +5474,7 @@
           <t>Mercy</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5375,6 +5482,7 @@
           <t>Shadow</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5382,6 +5490,7 @@
           <t>TheElements</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5389,6 +5498,7 @@
           <t>TheOpenHand</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5396,6 +5506,7 @@
           <t>Warrior</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5417,6 +5528,7 @@
           <t>Aasimar</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5424,6 +5536,7 @@
           <t>Abyss</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5431,6 +5544,7 @@
           <t>Abyssal</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5438,6 +5552,7 @@
           <t>Acheron</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5445,6 +5560,7 @@
           <t>Acolyte</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5452,6 +5568,7 @@
           <t>Artisan</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5459,6 +5576,7 @@
           <t>Benefit</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5466,6 +5584,7 @@
           <t>Carceri</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5473,6 +5592,7 @@
           <t>Charlatan</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5480,6 +5600,7 @@
           <t>Chromatic</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5487,6 +5608,7 @@
           <t>Chthonic</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5494,6 +5616,7 @@
           <t>Criminal</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5501,6 +5624,7 @@
           <t>DarkSun</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5508,6 +5632,7 @@
           <t>Demon</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5515,6 +5640,7 @@
           <t>Devil</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5522,6 +5648,7 @@
           <t>DragonLance</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5529,6 +5656,7 @@
           <t>Dragonborn</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5536,6 +5664,7 @@
           <t>Drow</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5543,6 +5672,7 @@
           <t>Dwarf</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5550,6 +5680,7 @@
           <t>Eberron</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5557,6 +5688,7 @@
           <t>Elf</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5564,6 +5696,7 @@
           <t>Entertainer</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5571,6 +5704,7 @@
           <t>Farmer</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5578,6 +5712,7 @@
           <t>Fey</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5585,6 +5720,7 @@
           <t>Feywild</t>
         </is>
       </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5592,6 +5728,7 @@
           <t>Gehenna</t>
         </is>
       </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5599,6 +5736,7 @@
           <t>Gnome</t>
         </is>
       </c>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -5606,6 +5744,7 @@
           <t>Goliath</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5613,6 +5752,7 @@
           <t>Guard</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5620,6 +5760,7 @@
           <t>Guide</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5627,6 +5768,7 @@
           <t>Hades</t>
         </is>
       </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5634,6 +5776,7 @@
           <t>Halfling</t>
         </is>
       </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5641,6 +5784,7 @@
           <t>Hermit</t>
         </is>
       </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5648,6 +5792,7 @@
           <t>HighElf</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5655,6 +5800,7 @@
           <t>Human</t>
         </is>
       </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5662,6 +5808,7 @@
           <t>LightfootHalfling</t>
         </is>
       </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5669,6 +5816,7 @@
           <t>LowerPlanes</t>
         </is>
       </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5676,6 +5824,7 @@
           <t>Merchant</t>
         </is>
       </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5683,6 +5832,7 @@
           <t>Metalic</t>
         </is>
       </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5690,6 +5840,7 @@
           <t>NineHells</t>
         </is>
       </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5697,6 +5848,7 @@
           <t>Noble</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5704,6 +5856,7 @@
           <t>Orc</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5711,6 +5864,7 @@
           <t>Pandemonium</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5718,6 +5872,7 @@
           <t>PlaneOfExistence</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5725,6 +5880,7 @@
           <t>Sage</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5732,6 +5888,7 @@
           <t>Sailor</t>
         </is>
       </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5739,6 +5896,7 @@
           <t>Scribe</t>
         </is>
       </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5746,6 +5904,7 @@
           <t>Soldier</t>
         </is>
       </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5753,6 +5912,7 @@
           <t>StrongheartHalfling</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5760,6 +5920,7 @@
           <t>Succubus</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5767,6 +5928,7 @@
           <t>Tiefling</t>
         </is>
       </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5774,6 +5936,7 @@
           <t>Underdark</t>
         </is>
       </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5781,6 +5944,7 @@
           <t>UpperPlanes</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5788,6 +5952,7 @@
           <t>Wayfarer</t>
         </is>
       </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5795,6 +5960,7 @@
           <t>WoodElf</t>
         </is>
       </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5802,6 +5968,7 @@
           <t>Yugoloth</t>
         </is>
       </c>
+      <c r="B56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5823,6 +5990,7 @@
           <t>AberrantSorcery</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5830,6 +5998,7 @@
           <t>ClockworkSorcery</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5837,6 +6006,7 @@
           <t>DraconicSorcery</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5844,6 +6014,7 @@
           <t>DragonResilience</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5851,6 +6022,7 @@
           <t>WildMagic</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6245,7 +6417,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Origin(Feat)</t>
         </is>
       </c>
     </row>
@@ -6451,6 +6623,7 @@
           <t>Abjurer</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6458,6 +6631,7 @@
           <t>Diviner</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6465,6 +6639,7 @@
           <t>Evoker</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6472,6 +6647,7 @@
           <t>Illusionist</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6479,6 +6655,7 @@
           <t>Spellbook</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6500,7 +6677,6 @@
           <t>Acid</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6508,7 +6684,6 @@
           <t>AlchemistsFire</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6516,7 +6691,6 @@
           <t>AlchemistsSupplies</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6524,7 +6698,6 @@
           <t>Ammunition</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6532,7 +6705,6 @@
           <t>Antitoxin</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6540,7 +6712,6 @@
           <t>ArcaneFocus</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6548,7 +6719,6 @@
           <t>Aristocrat</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6556,7 +6726,6 @@
           <t>Aristocratic</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6564,7 +6733,6 @@
           <t>Arrow</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6572,7 +6740,6 @@
           <t>Arrows</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6580,7 +6747,6 @@
           <t>ArtisansTools</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6588,7 +6754,6 @@
           <t>Attunment</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6596,7 +6761,6 @@
           <t>Backpack</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6604,7 +6768,6 @@
           <t>Bagpipes</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6612,7 +6775,6 @@
           <t>BallBearing</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6620,7 +6782,6 @@
           <t>Barrel</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6628,7 +6789,6 @@
           <t>BasicPoison</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6636,7 +6796,6 @@
           <t>Basket</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6644,7 +6803,6 @@
           <t>Battleaxe</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6652,7 +6810,6 @@
           <t>Bedroll</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6660,7 +6817,6 @@
           <t>Bell</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6668,7 +6824,6 @@
           <t>Blanket</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6676,7 +6831,6 @@
           <t>BlockAndTackle</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6696,7 +6850,6 @@
           <t>Bolt</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6704,7 +6857,6 @@
           <t>Bolts</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6712,7 +6864,6 @@
           <t>Book</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6720,7 +6871,6 @@
           <t>BootOfElvenkind</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6728,7 +6878,6 @@
           <t>BootOfStridingAndSpringing</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6736,7 +6885,6 @@
           <t>BottleGlass</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6744,7 +6892,6 @@
           <t>Breastplate</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6752,7 +6899,6 @@
           <t>BrewersSupplies</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6760,7 +6906,6 @@
           <t>Bucket</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6768,7 +6913,6 @@
           <t>Bullet</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6776,7 +6920,6 @@
           <t>BulletsFirearm</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6784,7 +6927,6 @@
           <t>BulletsSling</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6792,7 +6934,6 @@
           <t>BullseyeLantern</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6800,7 +6941,6 @@
           <t>BurglarsPack</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6808,7 +6948,6 @@
           <t>BurglersPack</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6816,7 +6955,6 @@
           <t>CP</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6824,7 +6962,6 @@
           <t>CP:%</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6832,7 +6969,6 @@
           <t>CaligraphersSupplies</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6840,7 +6976,6 @@
           <t>CalligraphersSupplies</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6860,7 +6995,6 @@
           <t>Candle</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6868,7 +7002,6 @@
           <t>CarpentersTools</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6876,7 +7009,6 @@
           <t>CartographersTools</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6884,7 +7016,6 @@
           <t>Case</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6892,7 +7023,6 @@
           <t>CaseCrossbowBolt</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6900,7 +7030,6 @@
           <t>CaseMapOrScroll</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6908,7 +7037,6 @@
           <t>Chain</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6916,7 +7044,6 @@
           <t>ChainMail</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6924,7 +7051,6 @@
           <t>ChainShirt</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6932,7 +7058,6 @@
           <t>Chest</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6940,7 +7065,6 @@
           <t>Cleave</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6948,7 +7072,6 @@
           <t>ClimbersKit</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6956,7 +7079,6 @@
           <t>ClothesFine</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6964,7 +7086,6 @@
           <t>ClothesTraveler</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6972,7 +7093,6 @@
           <t>ClothesTravelers</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6980,7 +7100,6 @@
           <t>Club</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6988,7 +7107,6 @@
           <t>CobblersTools</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6996,7 +7114,6 @@
           <t>Comfortable</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7004,7 +7121,6 @@
           <t>Component</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7012,7 +7128,6 @@
           <t>ComponentPouch</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7020,7 +7135,6 @@
           <t>CooksUtensils</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7028,7 +7142,6 @@
           <t>CopperPiece</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7036,7 +7149,6 @@
           <t>Costume</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7044,7 +7156,6 @@
           <t>Craft</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7052,7 +7163,6 @@
           <t>Crafting</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7060,7 +7170,6 @@
           <t>CraftingEquipment</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7068,7 +7177,6 @@
           <t>Crossbow</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7076,7 +7184,6 @@
           <t>CrossbowBoltCase</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7084,7 +7191,6 @@
           <t>Crowbar</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7092,7 +7198,6 @@
           <t>Curse</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7100,7 +7205,6 @@
           <t>Cursed</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7108,7 +7212,6 @@
           <t>Custome</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7128,7 +7231,6 @@
           <t>DamageThreshold</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7136,7 +7238,6 @@
           <t>Dart</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7144,7 +7245,6 @@
           <t>Dehyrdration</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7152,7 +7252,6 @@
           <t>Dice</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7160,7 +7259,6 @@
           <t>DiplomatsPack</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7168,7 +7266,6 @@
           <t>DisguiseKit</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7176,7 +7273,6 @@
           <t>Dragonchess</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7184,7 +7280,6 @@
           <t>DruidicFocus</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7192,7 +7287,6 @@
           <t>Drum</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7200,7 +7294,6 @@
           <t>Dulcimer</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7208,7 +7301,6 @@
           <t>DungeoneersPack</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7216,7 +7308,6 @@
           <t>EP</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7224,7 +7315,6 @@
           <t>ElectrumPiece</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7232,7 +7322,6 @@
           <t>EntertainersPack</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7240,7 +7329,6 @@
           <t>ExoticSaddle</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7248,7 +7336,6 @@
           <t>ExplorersPack</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7256,7 +7343,6 @@
           <t>FineClothes</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7264,7 +7350,6 @@
           <t>FirearmBullets</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7272,7 +7357,6 @@
           <t>Flail</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7280,7 +7364,6 @@
           <t>Flask</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7288,7 +7371,6 @@
           <t>Flute</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7296,7 +7378,6 @@
           <t>ForgeryKit</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7304,7 +7385,6 @@
           <t>GP</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7312,7 +7392,6 @@
           <t>GP:%</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7320,7 +7399,6 @@
           <t>GamingSet</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7328,7 +7406,6 @@
           <t>Glaive</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7336,7 +7413,6 @@
           <t>GlassBottle</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7344,7 +7420,6 @@
           <t>GlassblowersTools</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7352,7 +7427,6 @@
           <t>GoldPiece</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7360,7 +7434,6 @@
           <t>GrapplingHook</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7368,7 +7441,6 @@
           <t>Graze</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7388,7 +7460,6 @@
           <t>Greatclub</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7396,7 +7467,6 @@
           <t>Greatsword</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7404,7 +7474,6 @@
           <t>Halberd</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7412,7 +7481,6 @@
           <t>HalfPlateArmor</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7420,7 +7488,6 @@
           <t>HandCrossbow</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7428,7 +7495,6 @@
           <t>Handaxe</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7436,7 +7502,6 @@
           <t>HealersKit</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7444,7 +7509,6 @@
           <t>Heavy</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7452,7 +7516,6 @@
           <t>HeavyArmor</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7460,7 +7523,6 @@
           <t>HeavyCrossbow</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7468,7 +7530,6 @@
           <t>HerbalismKit</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7476,7 +7537,6 @@
           <t>HideArmor</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7484,7 +7544,6 @@
           <t>Hireling</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7504,7 +7563,6 @@
           <t>HolyWater</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7512,7 +7570,6 @@
           <t>HoodedLantern</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7520,7 +7577,6 @@
           <t>Horn</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7528,7 +7584,6 @@
           <t>HuntingTrap</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7536,7 +7591,6 @@
           <t>ImprovisedWeapons</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7544,7 +7598,6 @@
           <t>Ink</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7552,7 +7605,6 @@
           <t>InkPen</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7560,7 +7612,6 @@
           <t>IronPot</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7568,7 +7619,6 @@
           <t>IronSpikes</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7576,7 +7626,6 @@
           <t>Javelin</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7584,7 +7633,6 @@
           <t>Jug</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7592,7 +7640,6 @@
           <t>Keelboat</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7600,7 +7647,6 @@
           <t>LB:%</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7620,7 +7666,6 @@
           <t>Lamp</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7628,7 +7673,6 @@
           <t>Lance</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7648,7 +7692,6 @@
           <t>LanternBullseye</t>
         </is>
       </c>
-      <c r="B141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7656,7 +7699,6 @@
           <t>LanternHooded</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7664,7 +7706,6 @@
           <t>LeatherArmor</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7672,7 +7713,6 @@
           <t>LeatherworkersTools</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7680,7 +7720,6 @@
           <t>Light(Property)</t>
         </is>
       </c>
-      <c r="B145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7688,7 +7727,6 @@
           <t>LightArmor</t>
         </is>
       </c>
-      <c r="B146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7696,7 +7734,6 @@
           <t>LightCrossbow</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7704,7 +7741,6 @@
           <t>LightHammer</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7712,7 +7748,6 @@
           <t>Lighthammer</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7720,7 +7755,6 @@
           <t>Loading</t>
         </is>
       </c>
-      <c r="B150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7728,7 +7762,6 @@
           <t>Lock</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7748,7 +7781,6 @@
           <t>Longsword</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7756,7 +7788,6 @@
           <t>Lute</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7764,7 +7795,6 @@
           <t>Lyre</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7772,7 +7802,6 @@
           <t>Mace</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7780,7 +7809,6 @@
           <t>MagnifyingGlass</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7788,7 +7816,6 @@
           <t>Manacles</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7796,7 +7823,6 @@
           <t>Map</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7804,7 +7830,6 @@
           <t>MapOrScrollCase</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7812,7 +7837,6 @@
           <t>Martial</t>
         </is>
       </c>
-      <c r="B161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7820,7 +7844,6 @@
           <t>MasonsTools</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7828,7 +7851,6 @@
           <t>Mastery</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7836,7 +7858,6 @@
           <t>Maul</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7844,7 +7865,6 @@
           <t>MediumArmor</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7852,7 +7872,6 @@
           <t>Melee</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7860,7 +7879,6 @@
           <t>Mile:%</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7868,7 +7886,6 @@
           <t>MilitarySaddle</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7876,7 +7893,6 @@
           <t>Mirror</t>
         </is>
       </c>
-      <c r="B169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7884,7 +7900,6 @@
           <t>Modest</t>
         </is>
       </c>
-      <c r="B170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7892,7 +7907,6 @@
           <t>Morningstar</t>
         </is>
       </c>
-      <c r="B171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7900,7 +7914,6 @@
           <t>MusicalInstrument</t>
         </is>
       </c>
-      <c r="B172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7908,7 +7921,6 @@
           <t>Musket</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7916,7 +7928,6 @@
           <t>NavigatorsTools</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7924,7 +7935,6 @@
           <t>Needle</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7932,7 +7942,6 @@
           <t>Needles</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7940,7 +7949,6 @@
           <t>Net</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7948,7 +7956,6 @@
           <t>Nick</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7956,7 +7963,6 @@
           <t>Oil</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7964,7 +7970,6 @@
           <t>OneHanded</t>
         </is>
       </c>
-      <c r="B180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7972,7 +7977,6 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7980,7 +7984,6 @@
           <t>PaddedArmor</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7988,7 +7991,6 @@
           <t>PaintersSupplies</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7996,7 +7998,6 @@
           <t>PanFlute</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8004,7 +8005,6 @@
           <t>Paper</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8012,7 +8012,6 @@
           <t>Parchment</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8020,7 +8019,6 @@
           <t>Perfume</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8028,7 +8026,6 @@
           <t>Piercing</t>
         </is>
       </c>
-      <c r="B188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8036,7 +8033,6 @@
           <t>Pike</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8044,7 +8040,6 @@
           <t>Pistol</t>
         </is>
       </c>
-      <c r="B190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8052,7 +8047,6 @@
           <t>Piston</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8072,7 +8066,6 @@
           <t>PlatinumPiece</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8080,7 +8073,6 @@
           <t>PlayingCards</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8088,7 +8080,6 @@
           <t>Poison</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8096,7 +8087,6 @@
           <t>PoisonBasic</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8104,7 +8094,6 @@
           <t>PoisonersKit</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8112,7 +8101,6 @@
           <t>Pole</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8120,7 +8108,6 @@
           <t>Poor</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8128,7 +8115,6 @@
           <t>PortableRam</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8136,7 +8122,6 @@
           <t>PotIron</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8144,7 +8129,6 @@
           <t>Potion</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8164,7 +8148,6 @@
           <t>PotionsOfHealing</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8172,7 +8155,6 @@
           <t>PottersTools</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8180,7 +8162,6 @@
           <t>Pouch</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8188,7 +8169,6 @@
           <t>Pound:%</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8196,7 +8176,6 @@
           <t>PriestsPack</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8204,7 +8183,6 @@
           <t>Push</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8224,7 +8202,6 @@
           <t>Quiver</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8232,7 +8209,6 @@
           <t>RamPortable</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8240,7 +8216,6 @@
           <t>Range:%:%</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8248,7 +8223,6 @@
           <t>Ranged</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -8256,7 +8230,6 @@
           <t>RangedWeapons</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -8264,7 +8237,6 @@
           <t>Rapier</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8272,7 +8244,6 @@
           <t>Rations</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -8280,7 +8251,6 @@
           <t>Ring</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8288,7 +8258,6 @@
           <t>RingMail</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -8296,7 +8265,6 @@
           <t>RingOfFeatherFalling</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -8304,7 +8272,6 @@
           <t>RingOfProtection</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8312,7 +8279,6 @@
           <t>RingOfSwimming</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8320,7 +8286,6 @@
           <t>Robe</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -8328,7 +8293,6 @@
           <t>Rope</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -8336,7 +8300,6 @@
           <t>RowBoat</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -8344,7 +8307,6 @@
           <t>SP</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -8352,7 +8314,6 @@
           <t>SP:%</t>
         </is>
       </c>
-      <c r="B227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -8360,7 +8321,6 @@
           <t>Sack</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -8368,7 +8328,6 @@
           <t>Saddle</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -8376,7 +8335,6 @@
           <t>Sap</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -8384,7 +8342,6 @@
           <t>ScaleMail</t>
         </is>
       </c>
-      <c r="B231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -8392,7 +8349,6 @@
           <t>ScholarsPack</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -8400,7 +8356,6 @@
           <t>Scimitar</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -8408,7 +8363,6 @@
           <t>Scroll</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -8416,7 +8370,6 @@
           <t>Shawm</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -8424,7 +8377,6 @@
           <t>Shortbow</t>
         </is>
       </c>
-      <c r="B236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8432,7 +8384,6 @@
           <t>Shortsword</t>
         </is>
       </c>
-      <c r="B237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8440,7 +8391,6 @@
           <t>Shovel</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8448,7 +8398,6 @@
           <t>Sickle</t>
         </is>
       </c>
-      <c r="B239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8456,7 +8405,6 @@
           <t>SignalWhistle</t>
         </is>
       </c>
-      <c r="B240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8464,7 +8412,6 @@
           <t>SilverPiece</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8472,7 +8419,6 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8480,7 +8426,6 @@
           <t>Sling</t>
         </is>
       </c>
-      <c r="B243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8488,7 +8433,6 @@
           <t>SlingBullet</t>
         </is>
       </c>
-      <c r="B244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8496,7 +8440,6 @@
           <t>SmithsTools</t>
         </is>
       </c>
-      <c r="B245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8504,7 +8447,6 @@
           <t>Spear</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8512,7 +8454,6 @@
           <t>SpellCastingFocus</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8520,7 +8461,6 @@
           <t>SpellList</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8528,7 +8468,6 @@
           <t>SpellScroll</t>
         </is>
       </c>
-      <c r="B249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8536,7 +8475,6 @@
           <t>SpellScrolls</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8544,7 +8482,6 @@
           <t>SpikesIron</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8552,7 +8489,6 @@
           <t>SplintArmor</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8560,7 +8496,6 @@
           <t>Spyglass</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8568,7 +8503,6 @@
           <t>Squalid</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8576,7 +8510,6 @@
           <t>String</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8584,7 +8517,6 @@
           <t>StuddedLeatherArmor</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8592,7 +8524,6 @@
           <t>Tent</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8600,7 +8531,6 @@
           <t>ThivesTools</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8608,7 +8538,6 @@
           <t>ThreeDragonAnte</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8616,7 +8545,6 @@
           <t>Thrown</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8624,7 +8552,6 @@
           <t>Tinderbox</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8632,7 +8559,6 @@
           <t>TinkersTools</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8640,7 +8566,6 @@
           <t>Topple</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8660,7 +8585,6 @@
           <t>TravelersClothes</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8668,7 +8592,6 @@
           <t>Trident</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8676,7 +8599,6 @@
           <t>TwoHanded</t>
         </is>
       </c>
-      <c r="B267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8684,7 +8606,6 @@
           <t>Versatile</t>
         </is>
       </c>
-      <c r="B268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -8692,7 +8613,6 @@
           <t>Vex</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -8700,7 +8620,6 @@
           <t>Vial</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -8708,7 +8627,6 @@
           <t>Viol</t>
         </is>
       </c>
-      <c r="B271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -8716,7 +8634,6 @@
           <t>Wand</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -8724,7 +8641,6 @@
           <t>WarPick</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -8744,7 +8660,6 @@
           <t>Waterskin</t>
         </is>
       </c>
-      <c r="B275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8752,7 +8667,6 @@
           <t>Wealthy</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -8760,7 +8674,6 @@
           <t>WeaversTools</t>
         </is>
       </c>
-      <c r="B277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -8768,7 +8681,6 @@
           <t>Whip</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -8776,7 +8688,6 @@
           <t>WoodcarversTools</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -8784,7 +8695,6 @@
           <t>Wretched</t>
         </is>
       </c>
-      <c r="B280" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11603,7 +11513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11612,7 +11522,6 @@
           <t>AnimalSpeaker</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11620,7 +11529,6 @@
           <t>AspectOfTheWilds</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -11628,7 +11536,6 @@
           <t>BatteringRoots</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -11636,7 +11543,6 @@
           <t>Berserker</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -11644,7 +11550,6 @@
           <t>BoonOfIrresistableOffence</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11652,7 +11557,6 @@
           <t>BranchesOfTheTree</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11660,7 +11564,6 @@
           <t>BrutalStrike</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11668,7 +11571,6 @@
           <t>Concentration</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11676,7 +11578,6 @@
           <t>DangerSense</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11684,84 +11585,74 @@
           <t>DivineFury</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Emination:%</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>FanaticalFocus</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enemy</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>FastMovement</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FanaticalFocus</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>FeralInstincts</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FastMovement</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>Frenzy</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FeralInstincts</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>ImprovedBrutalStrike</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Force</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>IndomitableMight</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Frenzy</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>InstinctivePounce</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GreatAxe</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>IntimidatingPresence</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HitPointDie</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>MindlessRage</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Hover</t>
+          <t>NatureSpeaker</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -11769,127 +11660,112 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ImprovedBrutalStrike</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>Path</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IndomitableMight</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>PersistentRage</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Inititive</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>PowerOfTheWilds</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>InititiveRoll</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>PrimalChampion</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>InstinctivePounce</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>PrimalKnowledge</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IntimidatingPresence</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>Rage</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MindlessRage</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>RageDamage</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NaturSpeaker</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>RageOfTheGods</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Necrotic</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>RageOfTheWilds</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OuterPlanes</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>RecklessAttack</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Path</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>RelentlessRage</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PersistentRage</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>Retaliation</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PowerOfTheWilds</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>TravelAlongTheTree</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PrimalChampion</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>UnarmoredDefense</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PrimalKnowledge</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>VitalityOfTheTree</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Radiant</t>
+          <t>WarriorOfTheGods</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -11897,193 +11773,37 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rage</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>WeaponMastery</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RageDamage</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>WildHeart</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RageOfTheGods</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>WorldTree</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RageOfTheWilds</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>Zealot</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RecklessAttack</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>RelentlessRage</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Retaliation</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Ritual</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SavingThrowProficiencies</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SpellCastingAbility</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>StrengthSavingThrow</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>SubclassFeature</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>SwimnSpeed</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Tople</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>TravelAlongTheTree</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>UnarmoredDefence</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>UnarmoredDefense</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>VitalityOfTheTree</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>WarrionOfTheGods</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>WeaponMastery</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>WildHeart</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>WorldTree</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Zealot</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
           <t>ZealousPresence</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12112,7 +11832,6 @@
           <t>Assassin</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12144,7 +11863,6 @@
           <t>Soulknife</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12152,7 +11870,6 @@
           <t>Thief</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
